--- a/tests/testdata/excel/フォルダ/ダウンロード/ネットから取得.xlsx
+++ b/tests/testdata/excel/フォルダ/ダウンロード/ネットから取得.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{99D4AC0B-B878-4ABA-9988-B7A45D18755B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E4438D6-8A5B-4B32-B8DB-F70E3A13A1AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{8C1F87FD-EB49-429D-AF35-A32DF210719E}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{7FB36EB5-0E16-434F-A663-4029CCA5C955}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25DA5860-49D6-4B05-80C0-F5B470F36DE6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F6BBA4B-B89B-4C26-9C06-35698CC4C19F}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
